--- a/survey_templates/034_elf_character_assessment_survey--survey_templates.xlsx
+++ b/survey_templates/034_elf_character_assessment_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>elf_hair_color_black</t>
+          <t>elf hair color black</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>elf_hair_color_brown</t>
+          <t>elf hair color brown</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>elf_hair_color_blonde</t>
+          <t>elf hair color blonde</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>elf_hair_color_grey</t>
+          <t>elf hair color grey</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>elf_hair_color_red</t>
+          <t>elf hair color red</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>elf_eye_color_blue</t>
+          <t>elf eye color blue</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>elf_eye_color_brown</t>
+          <t>elf eye color brown</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>elf_eye_color_green</t>
+          <t>elf eye color green</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>elf_eye_color_grey</t>
+          <t>elf eye color grey</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>elf_eye_color_hazel</t>
+          <t>elf eye color hazel</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>elf_eye_color_red</t>
+          <t>elf eye color red</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>elf_eye_color_violet</t>
+          <t>elf eye color violet</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>elf_eye_color_yellow</t>
+          <t>elf eye color yellow</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>elf_skin_color_blue</t>
+          <t>elf skin color blue</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>elf_skin_color_grey</t>
+          <t>elf skin color grey</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>elf_skin_color_green</t>
+          <t>elf skin color green</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>elf_skin_color_red</t>
+          <t>elf skin color red</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>elf_skin_color_yellow</t>
+          <t>elf skin color yellow</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>elf_skin_color_white</t>
+          <t>elf skin color white</t>
         </is>
       </c>
     </row>
